--- a/CBT_2026_4회/산업안전기사_2026_4회_문항등록.xlsx
+++ b/CBT_2026_4회/산업안전기사_2026_4회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AI3" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Y-K(矢田部 · 木原) 성격검사&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;M 은 강하고 S 는 약하다&lt;/strong&gt;로 잡으면 두 개가 풀린다. &lt;strong&gt;C 는 빠르고 P 는 느리다&lt;/strong&gt;로 나머지 둘이 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;C 빠르고 P 느리고, M 강하고 S 약하다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Y-K(矢田部 · 木原) 성격검사&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;M은 강하고 S는 약하다&lt;/strong&gt;로 잡으면 두 개가 풀린다. &lt;strong&gt;C는 빠르고 P는 느리다&lt;/strong&gt;로 나머지 둘이 풀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;C 빠르고 P 느리고, M 강하고 S 약하다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
-          <t>① Man 은 사람 자신의 심리·생리·인간관계다.&lt;br&gt;② Machine 은 기계와 설비의 결함이다.&lt;br&gt;④ Management 는 관리 체제와 규정이다.</t>
+          <t>① Man은 사람 자신의 심리·생리·인간관계다.&lt;br&gt;② Machine은 기계와 설비의 결함이다.&lt;br&gt;④ Management는 관리 체제와 규정이다.</t>
         </is>
       </c>
       <c r="AI8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;4M 에 의한 재해 원인 분석&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Media 를 「매체」로 옮기면 헷갈린다&lt;/strong&gt;. 여기서는 &lt;strong&gt;작업 그 자체와 그 둘레&lt;/strong&gt;를 뜻한다고 새기는 편이 정확하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업정보 · 작업방법 · 작업환경 = Media&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;4M에 의한 재해 원인 분석&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Media를 「매체」로 옮기면 헷갈린다&lt;/strong&gt;. 여기서는 &lt;strong&gt;작업 그 자체와 그 둘레&lt;/strong&gt;를 뜻한다고 새기는 편이 정확하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업정보 · 작업방법 · 작업환경 = Media&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AG10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;혈액의 수분과 염분량&lt;/strong&gt;은 &lt;strong&gt;주간에 감소하고 야간에 상승&lt;/strong&gt; 한다. 나머지 셋은 모두 주간에 오르고 야간에 내린다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주간과 야간의 생체리듬&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;주간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;야간&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체온 · 혈압 · 맥박수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;혈액의 수분 · 염분량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;말초운동 기능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;혈액의 수분과 염분량&lt;/strong&gt;은 &lt;strong&gt;주간에 감소하고 야간에 상승&lt;/strong&gt;한다. 나머지 셋은 모두 주간에 오르고 야간에 내린다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주간과 야간의 생체리듬&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;주간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;야간&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체온 · 혈압 · 맥박수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;혈액의 수분 · 염분량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;말초운동 기능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상승&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH10" s="32" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AG15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;역할연기법(Role Playing)&lt;/strong&gt;이다. &lt;strong&gt;맡아서 연기해 보며&lt;/strong&gt; 자기 역할을 몸으로 익힌다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;집단 토의·학습 기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;어떻게 하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Symposium&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;여러 강사가 &lt;u&gt;주제를 나눠 발표&lt;/u&gt; 하고 질의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전문가 중심&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Panel Discussion&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;패널끼리 토의&lt;/u&gt; 한 뒤 청중과 질의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4~5명&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Forum&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;먼저 자료를 제시&lt;/u&gt; 하고 청중이 질문·토의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Buzz Session&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6명이 6분간&lt;/u&gt; 토의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;6-6 회의&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Brain Storming&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비판 없이 자유롭게&lt;/u&gt; 아이디어를 낸다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4원칙&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Role Playing&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;역할을 맡아 연기&lt;/u&gt; 한다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;체험 학습&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;역할연기법(Role Playing)&lt;/strong&gt;이다. &lt;strong&gt;맡아서 연기해 보며&lt;/strong&gt; 자기 역할을 몸으로 익힌다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;집단 토의·학습 기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;어떻게 하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Symposium&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;여러 강사가 &lt;u&gt;주제를 나눠 발표&lt;/u&gt;하고 질의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전문가 중심&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Panel Discussion&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;패널끼리 토의&lt;/u&gt;한 뒤 청중과 질의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4~5명&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Forum&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;먼저 자료를 제시&lt;/u&gt;하고 청중이 질문·토의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Buzz Session&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6명이 6분간&lt;/u&gt; 토의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;6-6 회의&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Brain Storming&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비판 없이 자유롭게&lt;/u&gt; 아이디어를 낸다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4원칙&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Role Playing&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;역할을 맡아 연기&lt;/u&gt;한다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;체험 학습&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH15" s="32" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="AG19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;종합재해지수(FSI)&lt;/strong&gt;다. $\mathrm{FSI} = \sqrt{\text{도수율} \times \text{강도율}}$ 로 &lt;strong&gt;얼마나 자주(도수율)&lt;/strong&gt;와 &lt;strong&gt;얼마나 크게(강도율)&lt;/strong&gt;를 하나로 묶는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해 지표&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율(FR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{재해건수} / \text{연근로시간} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 자주&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율(SR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{근로손실일수} / \text{연근로시간} \times 10^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 크게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종합재해지수(FSI)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\sqrt{\text{도수율} \times \text{강도율}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둘을 합쳐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{재해자수} / \text{평균근로자수} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;도수율 × 2.4&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_04_017_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;종합재해지수(FSI)&lt;/strong&gt;다. $\mathrm{FSI} = \sqrt{\text{도수율} \times \text{강도율}}$로 &lt;strong&gt;얼마나 자주(도수율)&lt;/strong&gt;와 &lt;strong&gt;얼마나 크게(강도율)&lt;/strong&gt;를 하나로 묶는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해 지표&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율(FR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{재해건수} / \text{연근로시간} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 자주&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율(SR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{근로손실일수} / \text{연근로시간} \times 10^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 크게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;종합재해지수(FSI)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\sqrt{\text{도수율} \times \text{강도율}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둘을 합쳐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{재해자수} / \text{평균근로자수} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;도수율 × 2.4&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2026_04_017_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
-          <t>① 강도율은 상해의 크기만 본다.&lt;br&gt;③ 안전활동율은 안전활동의 양을 재는 지표다.&lt;br&gt;④ Safe-T-Score 는 과거와 현재의 재해율을 견주는 지표다.</t>
+          <t>① 강도율은 상해의 크기만 본다.&lt;br&gt;③ 안전활동율은 안전활동의 양을 재는 지표다.&lt;br&gt;④ Safe-T-Score는 과거와 현재의 재해율을 견주는 지표다.</t>
         </is>
       </c>
       <c r="AI19" s="32" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AG20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;사전준비의 원칙&lt;/strong&gt;은 없다. 넷째는 &lt;strong&gt;예방가능의 원칙&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해예방의 4원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;함의&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손실우연의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;같은 사고라도 손실 크기는 우연&lt;/u&gt;이다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;손실이 작았다고 넘기면 안 된다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원인계기의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사고에는 반드시 원인&lt;/u&gt;이 있다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;원인은 여럿이 이어져 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;예방가능의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천재를 뺀 인재는 모두 막을 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 원칙이 안전관리의 전제다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대책선정의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원인에 맞는 대책&lt;/u&gt;이 반드시 있다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3E 로 세운다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;사전준비의 원칙&lt;/strong&gt;은 없다. 넷째는 &lt;strong&gt;예방가능의 원칙&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해예방의 4원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;함의&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손실우연의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;같은 사고라도 손실 크기는 우연&lt;/u&gt;이다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;손실이 작았다고 넘기면 안 된다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원인계기의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사고에는 반드시 원인&lt;/u&gt;이 있다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;원인은 여럿이 이어져 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;예방가능의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천재를 뺀 인재는 모두 막을 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 원칙이 안전관리의 전제다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대책선정의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원인에 맞는 대책&lt;/u&gt;이 반드시 있다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3E로 세운다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH20" s="32" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="U24" s="32" t="inlineStr">
         <is>
-          <t>그림과 같이 FTA로 분석된 시스템에서 현재 모든 기본사상에 대한 부품이 고장난 상태이다. 부품 X1부터 부품 X5 까지 순서대로 복구한다면 어느 부품을 수리 완료하는 시점에서 시스템이 정상가동 되는가?</t>
+          <t>그림과 같이 FTA로 분석된 시스템에서 현재 모든 기본사상에 대한 부품이 고장난 상태이다. 부품 X1부터 부품 X5까지 순서대로 복구한다면 어느 부품을 수리 완료하는 시점에서 시스템이 정상가동 되는가?</t>
         </is>
       </c>
       <c r="V24" s="32" t="inlineStr"/>
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>맨 위가 &lt;strong&gt;AND 게이트&lt;/strong&gt;이므로 &lt;strong&gt;아래 세 OR 가운데 하나만 0이 되면&lt;/strong&gt; 정상사상이 사라진다. 왼쪽 OR 는 $X_{1} + X_{2} + X_{3}$ 이라 &lt;strong&gt;셋을 다 고쳐야&lt;/strong&gt; 0이 된다. $X_{1} \rightarrow X_{2} \rightarrow X_{3}$ 순으로 고치면 &lt;strong&gt;X₃ 를 고치는 순간&lt;/strong&gt; 왼쪽 OR 가 0이 되어 시스템이 정상가동된다.&lt;img src="safe_A_2026_04_022_exp1.png"&gt;&lt;em&gt;AND 아래 OR 셋 — 한 갈래만 끊으면 정상으로 돌아온다&lt;/em&gt;</t>
+          <t>맨 위가 &lt;strong&gt;AND 게이트&lt;/strong&gt;이므로 &lt;strong&gt;아래 세 OR 가운데 하나만 0이 되면&lt;/strong&gt; 정상사상이 사라진다. 왼쪽 OR는 $X_{1} + X_{2} + X_{3}$이라 &lt;strong&gt;셋을 다 고쳐야&lt;/strong&gt; 0이 된다. $X_{1} \rightarrow X_{2} \rightarrow X_{3}$ 순으로 고치면 &lt;strong&gt;X₃ 를 고치는 순간&lt;/strong&gt; 왼쪽 OR가 0이 되어 시스템이 정상가동된다.&lt;img src="safe_A_2026_04_022_exp1.png"&gt;&lt;em&gt;AND 아래 OR 셋 — 한 갈래만 끊으면 정상으로 돌아온다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>① X₂ 까지 고쳐도 왼쪽 OR 에 X₃ 가 남아 여전히 1이다.&lt;br&gt;③ X₄ 는 가운데 OR 소속이라 이미 X₃ 에서 정상이 되었다.&lt;br&gt;④ X₅ 도 마찬가지로 이미 지난 뒤다.</t>
+          <t>① X₂ 까지 고쳐도 왼쪽 OR에 X₃ 가 남아 여전히 1이다.&lt;br&gt;③ X₄ 는 가운데 OR 소속이라 이미 X₃ 에서 정상이 되었다.&lt;br&gt;④ X₅ 도 마찬가지로 이미 지난 뒤다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FT도의 해석 — AND 와 OR&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AND 는 하나만 끊어도 전체가 끊긴다&lt;/strong&gt;. 그래서 복구 문제에서는 &lt;strong&gt;가장 먼저 0이 되는 갈래&lt;/strong&gt;를 찾으면 된다. 반대로 &lt;strong&gt;OR 는 하나만 남아도 살아 있다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND 아래는 한 갈래만 살리면 끝&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FT도의 해석 — AND와 OR&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AND는 하나만 끊어도 전체가 끊긴다&lt;/strong&gt;. 그래서 복구 문제에서는 &lt;strong&gt;가장 먼저 0이 되는 갈래&lt;/strong&gt;를 찾으면 된다. 반대로 &lt;strong&gt;OR는 하나만 남아도 살아 있다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND 아래는 한 갈래만 살리면 끝&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4301,17 +4301,17 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;수행 지연&lt;/strong&gt;은 &lt;strong&gt;timing error&lt;/strong&gt;다. &lt;strong&gt;commission error 는 「했지만 잘못한」&lt;/strong&gt; 오류다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;스웨인의 휴먼에러 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;우리말&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇인가&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;omission error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;해야 할 일을 &lt;u&gt;하지 않았다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;commission error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작위 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;했지만 잘못했다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;extraneous error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과잉행동 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하지 않아도 될 일&lt;/u&gt;을 했다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sequential error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서를 뒤바꿨다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;timing error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;너무 빠르거나 늦었다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;수행 지연&lt;/strong&gt;은 &lt;strong&gt;timing error&lt;/strong&gt;다. &lt;strong&gt;commission error는 「했지만 잘못한」&lt;/strong&gt; 오류다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;스웨인의 휴먼에러 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;우리말&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇인가&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;omission error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;해야 할 일을 &lt;u&gt;하지 않았다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;commission error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작위 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;했지만 잘못했다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;extraneous error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과잉행동 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하지 않아도 될 일&lt;/u&gt;을 했다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sequential error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서를 뒤바꿨다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;timing error&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간 오류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;너무 빠르거나 늦었다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
-          <t>① omission error 는 해야 할 일을 하지 않은 오류가 맞다.&lt;br&gt;③ extraneous error 는 불필요한 일을 한 오류가 맞다.&lt;br&gt;④ sequential error 는 순서 착오가 맞다.</t>
+          <t>① omission error는 해야 할 일을 하지 않은 오류가 맞다.&lt;br&gt;③ extraneous error는 불필요한 일을 한 오류가 맞다.&lt;br&gt;④ sequential error는 순서 착오가 맞다.</t>
         </is>
       </c>
       <c r="AI25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;스웨인(Swain)의 휴먼에러 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;commission 과 timing 을 바꿔치기&lt;/strong&gt; 하는 것이 이 유형의 단골 함정이다. &lt;strong&gt;「지연」이 보이면 timing&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안 함 · 잘못함 · 괜히 함 · 순서 바꿈 · 때를 놓침&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;스웨인(Swain)의 휴먼에러 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;commission과 timing을 바꿔치기&lt;/strong&gt;하는 것이 이 유형의 단골 함정이다. &lt;strong&gt;「지연」이 보이면 timing&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안 함 · 잘못함 · 괜히 함 · 순서 바꿈 · 때를 놓침&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AI26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인간-기계 시스템의 기능 배분&lt;/strong&gt;&lt;br&gt;가르는 물음 — &lt;strong&gt;처음 겪는 일을 다뤄야 하는가&lt;/strong&gt;. 예상 밖의 상황을 판단하고 원칙을 적용하는 것은 사람, &lt;strong&gt;정해진 것을 빠르고 정확히 되풀이&lt;/strong&gt; 하는 것은 기계다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람은 귀납, 기계는 연역&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인간-기계 시스템의 기능 배분&lt;/strong&gt;&lt;br&gt;가르는 물음 — &lt;strong&gt;처음 겪는 일을 다뤄야 하는가&lt;/strong&gt;. 예상 밖의 상황을 판단하고 원칙을 적용하는 것은 사람, &lt;strong&gt;정해진 것을 빠르고 정확히 되풀이&lt;/strong&gt;하는 것은 기계다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람은 귀납, 기계는 연역&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,11 @@
           <t>인간-기계 시스템에서 시스템의 설계를 다음과 같이 구분할 때 제3단계인 기본설계에 해당되지 않는 것은?</t>
         </is>
       </c>
-      <c r="V28" s="32" t="inlineStr"/>
+      <c r="V28" s="32" t="inlineStr">
+        <is>
+          <t>1단계 : 시스템의 목표와 성능 명세 결정&lt;br&gt;2단계 : 시스템의 정의&lt;br&gt;3단계 : 기본설계&lt;br&gt;4단계 : 인터페이스설계&lt;br&gt;5단계 : 보조물 설계&lt;br&gt;6단계 : 시험 및 평가</t>
+        </is>
+      </c>
       <c r="W28" s="32" t="inlineStr"/>
       <c r="X28" s="32" t="inlineStr">
         <is>
@@ -5071,17 +5075,17 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OTHER THAN&lt;/strong&gt;이다. &lt;strong&gt;완전히 다른 것으로 바뀐&lt;/strong&gt; 상태를 뜻한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;HAZOP 의 가이드워드&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가이드워드&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 가리키나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;NO / NOT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도의 완전한 부정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전혀 일어나지 않음&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MORE / LESS&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;양의 증가 또는 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;유량·압력·온도가 많거나 적음&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AS WELL AS&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의도한 것에 &lt;u&gt;덧붙여&lt;/u&gt; 다른 것도&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PART OF&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의도한 것의 &lt;u&gt;일부만&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;REVERSE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도와 반대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;역류&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OTHER THAN&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;완전한 대체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전혀 다른 것&lt;/u&gt;으로 바뀜&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;OTHER THAN&lt;/strong&gt;이다. &lt;strong&gt;완전히 다른 것으로 바뀐&lt;/strong&gt; 상태를 뜻한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;HAZOP의 가이드워드&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가이드워드&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 가리키나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;NO / NOT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도의 완전한 부정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전혀 일어나지 않음&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MORE / LESS&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;양의 증가 또는 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;유량·압력·온도가 많거나 적음&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AS WELL AS&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의도한 것에 &lt;u&gt;덧붙여&lt;/u&gt; 다른 것도&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PART OF&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의도한 것의 &lt;u&gt;일부만&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;REVERSE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도와 반대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;역류&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OTHER THAN&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;완전한 대체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전혀 다른 것&lt;/u&gt;으로 바뀜&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① NOT 은 설계 의도의 완전한 부정이다.&lt;br&gt;② REVERSE 는 설계 의도와 반대다.&lt;br&gt;③ PART OF 는 성질상의 감소, 곧 일부만 이루어진 상태다.</t>
+          <t>① NOT은 설계 의도의 완전한 부정이다.&lt;br&gt;② REVERSE는 설계 의도와 반대다.&lt;br&gt;③ PART OF는 성질상의 감소, 곧 일부만 이루어진 상태다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;HAZOP 의 가이드워드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AS WELL AS 와 PART OF 는 양이 아니라 성질&lt;/strong&gt;을 말한다. &lt;strong&gt;MORE/LESS 가 양&lt;/strong&gt; 쪽이다. 이 대비가 가장 자주 물어진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;완전히 다른 것 = OTHER THAN&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;HAZOP의 가이드워드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AS WELL AS와 PART OF는 양이 아니라 성질&lt;/strong&gt;을 말한다. &lt;strong&gt;MORE/LESS가 양&lt;/strong&gt; 쪽이다. 이 대비가 가장 자주 물어진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;완전히 다른 것 = OTHER THAN&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5175,7 @@
       </c>
       <c r="V32" s="32" t="inlineStr">
         <is>
-          <t>설비를 새로 계획·설계하는 단계에서 신기술을 기초로 신뢰성, 조작성, 보전성, 안전성, 경제성 등이 우수한 설비의 선정·조달 또는 설계를 통하여 궁극적으로 설비의 보전 불필요의 체제를 목표로 한 설비보전 방법을 말한다.</t>
+          <t>설비보전 정보와 신기술을 기초로 신뢰성, 조작성, 보전성, 안전성, 경제성 등이 우수한 설비의 선정, 조달 또는 설계를 통하여 궁극적으로 설비의 설계, 제작 단계에서 보전활동이 불필요한 체제를 목표로 한 설비보전 방법을 말한다.</t>
         </is>
       </c>
       <c r="W32" s="32" t="inlineStr"/>
@@ -5333,12 +5337,12 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>직렬은 곱한다. $0.6 \times 0.9 = 0.54$ 다.&lt;img src="safe_A_2026_04_031_exp1.png"&gt;&lt;em&gt;직렬과 병렬 — 하나만 고장 나도 멈추면 직렬이다&lt;/em&gt;</t>
+          <t>직렬은 곱한다. $0.6 \times 0.9 = 0.54$다.&lt;img src="safe_A_2026_04_031_exp1.png"&gt;&lt;em&gt;직렬과 병렬 — 하나만 고장 나도 멈추면 직렬이다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① 0.32 는 계산과 맞지 않는다.&lt;br&gt;③ 0.75 도 맞지 않는다.&lt;br&gt;④ 0.96 은 병렬로 계산한 값 $1 - ( 1 - 0.6 ) ( 1 - 0.9 ) = 0.96$ 이다.</t>
+          <t>① 0.32는 계산과 맞지 않는다.&lt;br&gt;③ 0.75 도 맞지 않는다.&lt;br&gt;④ 0.96은 병렬로 계산한 값 $1 - ( 1 - 0.6 ) ( 1 - 0.9 ) = 0.96$이다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
@@ -5720,12 +5724,12 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;다습한 환경&lt;/strong&gt;은 CTD 의 인자가 아니다. 온도 인자로는 &lt;strong&gt;저온&lt;/strong&gt;이 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누적손상장애(CTD)의 발생인자&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반복도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;같은 동작의 되풀이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조립 · 타이핑&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무리한 힘&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과도한 힘&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;무거운 것 쥐기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부적절한 자세&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관절이 꺾인 자세&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;손목을 꺾은 채 작업&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;진동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;장시간의 진동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전동공구&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차가운 환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다습이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;다습한 환경&lt;/strong&gt;은 CTD의 인자가 아니다. 온도 인자로는 &lt;strong&gt;저온&lt;/strong&gt;이 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누적손상장애(CTD)의 발생인자&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인자&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반복도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;같은 동작의 되풀이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조립 · 타이핑&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무리한 힘&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과도한 힘&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;무거운 것 쥐기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부적절한 자세&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관절이 꺾인 자세&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;손목을 꺾은 채 작업&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;진동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;장시간의 진동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전동공구&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저온&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차가운 환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다습이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>① 무리한 힘은 CTD 의 인자다.&lt;br&gt;③ 장시간의 진동도 인자다.&lt;br&gt;④ 반복도가 높은 작업도 인자다.</t>
+          <t>① 무리한 힘은 CTD의 인자다.&lt;br&gt;③ 장시간의 진동도 인자다.&lt;br&gt;④ 반복도가 높은 작업도 인자다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
@@ -5988,7 +5992,7 @@
       </c>
       <c r="AI38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;피츠의 법칙(Fitts' Law)&lt;/strong&gt;&lt;br&gt;$D$ 는 거리, $W$ 는 표적의 폭이다. &lt;strong&gt;거리가 멀수록 · 표적이 좁을수록 오래 걸린다&lt;/strong&gt;. 화면에서 중요한 버튼을 크게 만드는 근거가 이 법칙이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;커서 이동시간이면 피츠&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;피츠의 법칙(Fitts' Law)&lt;/strong&gt;&lt;br&gt;$D$는 거리, $W$는 표적의 폭이다. &lt;strong&gt;거리가 멀수록 · 표적이 좁을수록 오래 걸린다&lt;/strong&gt;. 화면에서 중요한 버튼을 크게 만드는 근거가 이 법칙이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;커서 이동시간이면 피츠&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6107,17 +6111,17 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>배경 휘도는 $L_{b} = \text{반사율} \times \text{조도} / \pi = 0.85 \times 350 / \pi \fallingdotseq 94.7$ [cd/m²] 다. 글자 부분의 휘도는 배경에 글자 밝기를 더한 $94.7 + 400 = 494.7$ 이다. $\text{대비} = ( L_{b} - L_{t} ) / L_{b} = ( 94.7 - 494.7 ) / 94.7 \fallingdotseq - 4.2$ 다.</t>
+          <t>배경 휘도는 $L_{b} = \text{반사율} \times \text{조도} / \pi = 0.85 \times 350 / \pi \fallingdotseq 94.7$ [cd/m²]다. 글자 부분의 휘도는 배경에 글자 밝기를 더한 $94.7 + 400 = 494.7$이다. $\text{대비} = ( L_{b} - L_{t} ) / L_{b} = ( 94.7 - 494.7 ) / 94.7 \fallingdotseq - 4.2$다.</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>① −6.0 은 계산과 맞지 않는다.&lt;br&gt;② −5.0 도 맞지 않는다.&lt;br&gt;④ −2.8 도 맞지 않는다.</t>
+          <t>① −6.0은 계산과 맞지 않는다.&lt;br&gt;② −5.0 도 맞지 않는다.&lt;br&gt;④ −2.8 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;대비(contrast)&lt;/strong&gt;&lt;br&gt;$\text{대비} = ( L_{b} - L_{t} ) / L_{b} \times 100$ 이다. &lt;strong&gt;배경보다 글자가 밝으면 대비가 음수&lt;/strong&gt;로 나온다. 화면처럼 스스로 빛을 내는 표시장치가 그렇다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휘도 = 반사율 × 조도 ÷ &lt;/u&gt;$\pi$ — 원주율로 나누는 것을 잊기 쉽다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;대비(contrast)&lt;/strong&gt;&lt;br&gt;$\text{대비} = ( L_{b} - L_{t} ) / L_{b} \times 100$이다. &lt;strong&gt;배경보다 글자가 밝으면 대비가 음수&lt;/strong&gt;로 나온다. 화면처럼 스스로 빛을 내는 표시장치가 그렇다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휘도 = 반사율 × 조도 ÷ &lt;/u&gt;$\pi$ — 원주율로 나누는 것을 잊기 쉽다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7526,17 +7530,17 @@
       </c>
       <c r="AG50" s="32" t="inlineStr">
         <is>
-          <t>$Y = 6 + 0.15 X$ 다. $6 + 0.15 \times 100 = 21$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가드 개구부의 안전간격&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;X &amp;lt; 160 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.15 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;X 는 가드와 위험점 사이의 거리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;X ≥ 160 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 30$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 멀어져도 30 에서 멈춘다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.1 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;계수가 0.1&lt;/u&gt;로 더 엄격&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$Y = 6 + 0.15 X$다. $6 + 0.15 \times 100 = 21$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가드 개구부의 안전간격&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;X &amp;lt; 160 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.15 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;X는 가드와 위험점 사이의 거리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;X ≥ 160 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 30$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 멀어져도 30에서 멈춘다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.1 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;계수가 0.1&lt;/u&gt;로 더 엄격&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>① 11 [mm] 는 계수를 잘못 잡았을 때 나온다.&lt;br&gt;③ 26 [mm] 도 계산과 맞지 않는다.&lt;br&gt;④ 31 [mm] 은 X 가 160 [mm] 이상일 때의 30 에 가깝다.</t>
+          <t>① 11 [mm]는 계수를 잘못 잡았을 때 나온다.&lt;br&gt;③ 26 [mm] 도 계산과 맞지 않는다.&lt;br&gt;④ 31 [mm]은 X가 160 [mm] 이상일 때의 30에 가깝다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;ILO 규정 — 가드 개구부의 안전간격&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;멀수록 틈을 넓게 두어도 된다&lt;/strong&gt;는 뜻이다. 손이 들어가더라도 위험점에 닿지 못하기 때문이다. 다만 &lt;strong&gt;160 [mm] 를 넘으면 30 [mm] 에서 멈춘다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Y = 6 + 0.15 X$ — &lt;u&gt;전동체면 0.1&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;ILO 규정 — 가드 개구부의 안전간격&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;멀수록 틈을 넓게 두어도 된다&lt;/strong&gt;는 뜻이다. 손이 들어가더라도 위험점에 닿지 못하기 때문이다. 다만 &lt;strong&gt;160 [mm]를 넘으면 30 [mm]에서 멈춘다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Y = 6 + 0.15 X$ — &lt;u&gt;전동체면 0.1&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8051,7 @@
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
-          <t>① fail safe 는 기계가 고장 났을 때 안전한 쪽으로 작동하는 것이다.&lt;br&gt;② fail active 는 페일 세이프의 한 단계로 잠시 운전을 이어 가는 것이다.&lt;br&gt;③ fail operational 은 다음 검사까지 운전이 가능한 가장 높은 단계다.</t>
+          <t>① fail safe는 기계가 고장 났을 때 안전한 쪽으로 작동하는 것이다.&lt;br&gt;② fail active는 페일 세이프의 한 단계로 잠시 운전을 이어 가는 것이다.&lt;br&gt;③ fail operational은 다음 검사까지 운전이 가능한 가장 높은 단계다.</t>
         </is>
       </c>
       <c r="AI54" s="32" t="inlineStr">
@@ -8568,7 +8572,7 @@
       </c>
       <c r="AI58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;음향방출시험(AE, Acoustic Emission)&lt;/strong&gt;&lt;br&gt;다른 비파괴검사가 &lt;strong&gt;이미 생긴 결함&lt;/strong&gt;을 찾는 데 견주어, &lt;strong&gt;음향방출시험은 지금 자라고 있는 균열&lt;/strong&gt;을 잡아낸다. 그래서 &lt;strong&gt;사용 중인 설비를 실시간으로 감시&lt;/strong&gt; 할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;스스로 내는 소리를 들으면 음향방출&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;음향방출시험(AE, Acoustic Emission)&lt;/strong&gt;&lt;br&gt;다른 비파괴검사가 &lt;strong&gt;이미 생긴 결함&lt;/strong&gt;을 찾는 데 견주어, &lt;strong&gt;음향방출시험은 지금 자라고 있는 균열&lt;/strong&gt;을 잡아낸다. 그래서 &lt;strong&gt;사용 중인 설비를 실시간으로 감시&lt;/strong&gt;할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;스스로 내는 소리를 들으면 음향방출&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8821,7 +8825,7 @@
       </c>
       <c r="AH60" s="32" t="inlineStr">
         <is>
-          <t>① 0.1 [m] 는 기준이 아니다.&lt;br&gt;② 0.15 [m] 도 아니다.&lt;br&gt;④ 0.3 [m] 도 기준이 아니다.</t>
+          <t>① 0.1 [m]는 기준이 아니다.&lt;br&gt;② 0.15 [m] 도 아니다.&lt;br&gt;④ 0.3 [m] 도 기준이 아니다.</t>
         </is>
       </c>
       <c r="AI60" s="32" t="inlineStr">
@@ -9203,17 +9207,17 @@
       </c>
       <c r="AG63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;사용전압 50 [V] 를 넘으면&lt;/strong&gt; 누전차단기를 달아야 한다. 50 [V] 아래는 감전되어도 위험이 낮다고 본다.</t>
+          <t>&lt;strong&gt;사용전압 50 [V]를 넘으면&lt;/strong&gt; 누전차단기를 달아야 한다. 50 [V] 아래는 감전되어도 위험이 낮다고 본다.</t>
         </is>
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>① 30 [V] 는 우리나라의 안전전압이지 누전차단기 시설의 기준이 아니다.&lt;br&gt;③ 90 [V] 라는 기준은 없다.&lt;br&gt;④ 150 [V] 는 접지 대상과 접지 생략의 기준이다.</t>
+          <t>① 30 [V]는 우리나라의 안전전압이지 누전차단기 시설의 기준이 아니다.&lt;br&gt;③ 90 [V]라는 기준은 없다.&lt;br&gt;④ 150 [V]는 접지 대상과 접지 생략의 기준이다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;한국전기설비규정(KEC) 211.2.4 — 누전차단기의 시설&lt;/strong&gt;&lt;br&gt;세 숫자를 갈라 둔다 — &lt;strong&gt;30 [V] 는 안전전압&lt;/strong&gt;, &lt;strong&gt;50 [V] 초과는 누전차단기 시설 대상&lt;/strong&gt;, &lt;strong&gt;150 [V] 초과는 접지 대상&lt;/strong&gt;. 셋이 자주 섞여 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;50 [V] 넘으면 누전차단기&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;한국전기설비규정(KEC) 211.2.4 — 누전차단기의 시설&lt;/strong&gt;&lt;br&gt;세 숫자를 갈라 둔다 — &lt;strong&gt;30 [V]는 안전전압&lt;/strong&gt;, &lt;strong&gt;50 [V] 초과는 누전차단기 시설 대상&lt;/strong&gt;, &lt;strong&gt;150 [V] 초과는 접지 대상&lt;/strong&gt;. 셋이 자주 섞여 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;50 [V] 넘으면 누전차단기&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9332,17 +9336,17 @@
       </c>
       <c r="AG64" s="32" t="inlineStr">
         <is>
-          <t>$W = I^{2} R T$ 다. $I = 165 / \sqrt{T}$ [mA] 이므로 $W = ( 165 \times 10^{-3} / \sqrt{T} )^{2} \times 500 \times T$ 다. $T$ 가 약분되어 $W = 165^{2} \times 10^{-6} \times 500 = 0.027225 \times 500 \fallingdotseq 13.6$ [J] 다.</t>
+          <t>$W = I^{2} R T$다. $I = 165 / \sqrt{T}$ [mA]이므로 $W = ( 165 \times 10^{-3} / \sqrt{T} )^{2} \times 500 \times T$다. $T$가 약분되어 $W = 165^{2} \times 10^{-6} \times 500 = 0.027225 \times 500 \fallingdotseq 13.6$ [J]다.</t>
         </is>
       </c>
       <c r="AH64" s="32" t="inlineStr">
         <is>
-          <t>① 9.8 [J] 는 저항을 작게 잡았을 때 쪽이다.&lt;br&gt;③ 19.6 [J] 는 계산과 맞지 않는다.&lt;br&gt;④ 27 [J] 는 저항 500 을 곱하지 않은 값에 가깝다.</t>
+          <t>① 9.8 [J]는 저항을 작게 잡았을 때 쪽이다.&lt;br&gt;③ 19.6 [J]는 계산과 맞지 않는다.&lt;br&gt;④ 27 [J]는 저항 500을 곱하지 않은 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI64" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;심실세동 한계에너지&lt;/strong&gt;&lt;br&gt;핵심은 &lt;strong&gt;통전시간 &lt;/strong&gt;$T$&lt;strong&gt; 가 약분되어 사라진다&lt;/strong&gt;는 점이다. 그래서 &lt;strong&gt;시간과 무관하게 약 13.6 [J]&lt;/strong&gt;이라는 하나의 값이 나온다. 이것이 &lt;strong&gt;감전의 위험한계에너지&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;T 가 약분된다&lt;/u&gt; — 답은 13.6 [J] 하나.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;심실세동 한계에너지&lt;/strong&gt;&lt;br&gt;핵심은 &lt;strong&gt;통전시간 &lt;/strong&gt;$T$&lt;strong&gt;가 약분되어 사라진다&lt;/strong&gt;는 점이다. 그래서 &lt;strong&gt;시간과 무관하게 약 13.6 [J]&lt;/strong&gt;이라는 하나의 값이 나온다. 이것이 &lt;strong&gt;감전의 위험한계에너지&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;T가 약분된다&lt;/u&gt; — 답은 13.6 [J] 하나.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9733,7 @@
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감전사고의 방지대책&lt;/strong&gt;&lt;br&gt;충전부 방호의 다섯 가지 — &lt;strong&gt;절연물로 감싼다 · 폐쇄형 외함 · 방호망이나 절연 덮개 · 대지전압 30 [V] 이하 · 출입이 어려운 곳에 두고 위험표시&lt;/strong&gt;. &lt;strong&gt;모두 「전기가 안 통하게」&lt;/strong&gt; 하는 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;통전망이 아니라 절연망&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;감전사고의 방지대책&lt;/strong&gt;&lt;br&gt;충전부 방호의 다섯 가지 — &lt;strong&gt;절연물로 감싼다 · 폐쇄형 외함 · 방호망이나 절연 덮개 · 대지전압 30 [V] 이하 · 출입이 어려운 곳에 두고 위험표시&lt;/strong&gt;. &lt;strong&gt;모두 「전기가 안 통하게」&lt;/strong&gt;하는 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;통전망이 아니라 절연망&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9969,17 +9973,17 @@
       </c>
       <c r="AG69" s="32" t="inlineStr">
         <is>
-          <t>$H = 0.24 I^{2} R t$ 다. $0.24 \times 5^{2} \times 20 \times 180 = 0.24 \times 25 \times 20 \times 180 = 21 {,} 600$ [cal] 이다.</t>
+          <t>$H = 0.24 I^{2} R t$다. $0.24 \times 5^{2} \times 20 \times 180 = 0.24 \times 25 \times 20 \times 180 = 21 {,} 600$ [cal]이다.</t>
         </is>
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 4,320 은 전류를 제곱하지 않았을 때 나온다.&lt;br&gt;② 90,000 은 0.24 를 곱하지 않은 [J] 값이다.&lt;br&gt;④ 376,560 은 자릿수가 어긋난다.</t>
+          <t>① 4,320은 전류를 제곱하지 않았을 때 나온다.&lt;br&gt;② 90,000은 0.24를 곱하지 않은 [J] 값이다.&lt;br&gt;④ 376,560은 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;줄의 법칙(Joule's law)&lt;/strong&gt;&lt;br&gt;$H = I^{2} R t$ [J] 이고, &lt;strong&gt;[cal] 로 바꾸려면 0.24 를 곱한다&lt;/strong&gt;. 시간은 &lt;strong&gt;반드시 초로&lt;/strong&gt; 바꿔야 한다 — 3분은 180초다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.24 곱하고, 분은 초로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;줄의 법칙(Joule's law)&lt;/strong&gt;&lt;br&gt;$H = I^{2} R t$ [J]이고, &lt;strong&gt;[cal]로 바꾸려면 0.24를 곱한다&lt;/strong&gt;. 시간은 &lt;strong&gt;반드시 초로&lt;/strong&gt; 바꿔야 한다 — 3분은 180초다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.24 곱하고, 분은 초로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10104,7 @@
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;KS C IEC 60079-0 — 방폭기기의 표준 주위온도&lt;/strong&gt;&lt;br&gt;이 범위를 벗어난 곳에서 쓰려면 &lt;strong&gt;인증번호에 접미사 X&lt;/strong&gt;를 붙여 특정사용조건을 명시해야 한다. 그래서 문항 단서에 「X 표시가 없는 기기」라고 못박은 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;−20 에서 +40 까지&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;KS C IEC 60079-0 — 방폭기기의 표준 주위온도&lt;/strong&gt;&lt;br&gt;이 범위를 벗어난 곳에서 쓰려면 &lt;strong&gt;인증번호에 접미사 X&lt;/strong&gt;를 붙여 특정사용조건을 명시해야 한다. 그래서 문항 단서에 「X 표시가 없는 기기」라고 못박은 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;−20에서 +40까지&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10606,17 +10610,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$V = \sqrt{2 W / C}$ 다. $V = \sqrt{2 \times 0.019 \times 10^{-3} / ( 1 {,} 000 \times 10^{-12} )} = \sqrt{3.8 \times 10^{4}} \fallingdotseq 195$ [V] 다.</t>
+          <t>$V = \sqrt{2 W / C}$다. $V = \sqrt{2 \times 0.019 \times 10^{-3} / ( 1 {,} 000 \times 10^{-12} )} = \sqrt{3.8 \times 10^{4}} \fallingdotseq 195$ [V]다.</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 3,900 [V] 는 자릿수가 크게 어긋난다.&lt;br&gt;② 1,950 [V] 는 10배 어긋난다.&lt;br&gt;③ 390 [V] 는 2배 어긋난다.</t>
+          <t>① 3,900 [V]는 자릿수가 크게 어긋난다.&lt;br&gt;② 1,950 [V]는 10배 어긋난다.&lt;br&gt;③ 390 [V]는 2배 어긋난다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 에너지와 착화한계전압&lt;/strong&gt;&lt;br&gt;$W = \dfrac{1}{2} C V^{2}$ 을 $V$ 에 대해 푼 것이다. &lt;strong&gt;[mJ] 는 &lt;/strong&gt;$10^{-3}$&lt;strong&gt;, [pF] 는 &lt;/strong&gt;$10^{-12}$로 바꾸는 자리에서 자릿수를 놓치기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \sqrt{2 W / C}$ — &lt;u&gt;단위를 [J] 와 [F] 로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 에너지와 착화한계전압&lt;/strong&gt;&lt;br&gt;$W = \dfrac{1}{2} C V^{2}$을 $V$에 대해 푼 것이다. &lt;strong&gt;[mJ]는 &lt;/strong&gt;$10^{-3}$&lt;strong&gt;, [pF]는 &lt;/strong&gt;$10^{-12}$로 바꾸는 자리에서 자릿수를 놓치기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \sqrt{2 W / C}$ — &lt;u&gt;단위를 [J]와 [F]로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11122,12 +11126,12 @@
       </c>
       <c r="AG78" s="32" t="inlineStr">
         <is>
-          <t>$\text{여유도} = \dfrac{\text{충격절연강도} - \text{제한전압}}{\text{제한전압}} \times 100$ 이다. $( 1 {,} 050 - 752 ) / 752 \times 100 = 298 / 752 \times 100 \fallingdotseq 39.6 \fallingdotseq 40$ [%] 다.</t>
+          <t>$\text{여유도} = \dfrac{\text{충격절연강도} - \text{제한전압}}{\text{제한전압}} \times 100$이다. $( 1 {,} 050 - 752 ) / 752 \times 100 = 298 / 752 \times 100 \fallingdotseq 39.6 \fallingdotseq 40$ [%]다.</t>
         </is>
       </c>
       <c r="AH78" s="32" t="inlineStr">
         <is>
-          <t>① 18 [%] 는 계산과 맞지 않는다.&lt;br&gt;② 28 [%] 는 분모를 충격절연강도로 잡았을 때에 가깝다.&lt;br&gt;④ 43 [%] 도 맞지 않는다.</t>
+          <t>① 18 [%]는 계산과 맞지 않는다.&lt;br&gt;② 28 [%]는 분모를 충격절연강도로 잡았을 때에 가깝다.&lt;br&gt;④ 43 [%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI78" s="32" t="inlineStr">
@@ -11652,7 +11656,7 @@
       </c>
       <c r="AI82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제전기의 종류&lt;/strong&gt;&lt;br&gt;제전기는 &lt;strong&gt;공기를 이온화해 반대 극성 이온으로 전하를 중화&lt;/strong&gt; 한다. 접지와 달리 &lt;strong&gt;부도체에도 통한다&lt;/strong&gt;는 것이 가장 큰 장점이며, 설치 시 &lt;strong&gt;제전효율 90 [%] 이상&lt;/strong&gt; 이어야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전압인가 · 자기방전 · 방사선&lt;/u&gt; 셋.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;제전기의 종류&lt;/strong&gt;&lt;br&gt;제전기는 &lt;strong&gt;공기를 이온화해 반대 극성 이온으로 전하를 중화&lt;/strong&gt;한다. 접지와 달리 &lt;strong&gt;부도체에도 통한다&lt;/strong&gt;는 것이 가장 큰 장점이며, 설치 시 &lt;strong&gt;제전효율 90 [%] 이상&lt;/strong&gt; 이어야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전압인가 · 자기방전 · 방사선&lt;/u&gt; 셋.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11900,17 +11904,17 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>$T_{2} = T_{1} ( P_{2} / P_{1} )^{( k - 1 ) / k}$ 다. $T_{1} = 293$ [K] 이고 $( k - 1 ) / k = 0.4 / 1.4 = 0.2857$ 이므로 $T_{2} = 293 \times 3^{0.2857} = 293 \times 1.369 \fallingdotseq 401$ [K] = &lt;strong&gt;128 [℃]&lt;/strong&gt;다.</t>
+          <t>$T_{2} = T_{1} ( P_{2} / P_{1} )^{( k - 1 ) / k}$다. $T_{1} = 293$ [K]이고 $( k - 1 ) / k = 0.4 / 1.4 = 0.2857$이므로 $T_{2} = 293 \times 3^{0.2857} = 293 \times 1.369 \fallingdotseq 401$ [K] = &lt;strong&gt;128 [℃]&lt;/strong&gt;다.</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
         <is>
-          <t>① 68 [℃] 는 지수를 잘못 잡았을 때 쪽이다.&lt;br&gt;② 75 [℃] 도 계산과 맞지 않는다.&lt;br&gt;④ 164 [℃] 는 지수를 크게 잡았을 때 나온다.</t>
+          <t>① 68 [℃]는 지수를 잘못 잡았을 때 쪽이다.&lt;br&gt;② 75 [℃] 도 계산과 맞지 않는다.&lt;br&gt;④ 164 [℃]는 지수를 크게 잡았을 때 나온다.</t>
         </is>
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;단열압축과 온도 상승&lt;/strong&gt;&lt;br&gt;반드시 &lt;strong&gt;절대온도 [K] 로 바꿔 계산&lt;/strong&gt; 한 뒤 다시 [℃] 로 돌린다. 압축기 토출부가 뜨거워지는 것, 디젤엔진이 점화플러그 없이 착화하는 것이 모두 이 원리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T_{2} = T_{1} ( P_{2} / P_{1} )^{( k - 1 ) / k}$ — &lt;u&gt;켈빈으로 계산&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;단열압축과 온도 상승&lt;/strong&gt;&lt;br&gt;반드시 &lt;strong&gt;절대온도 [K]로 바꿔 계산&lt;/strong&gt;한 뒤 다시 [℃]로 돌린다. 압축기 토출부가 뜨거워지는 것, 디젤엔진이 점화플러그 없이 착화하는 것이 모두 이 원리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T_{2} = T_{1} ( P_{2} / P_{1} )^{( k - 1 ) / k}$ — &lt;u&gt;켈빈으로 계산&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12029,12 +12033,12 @@
       </c>
       <c r="AG85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;벤젠의 인화점은 −11 [℃]&lt;/strong&gt;로 0 [℃] 보다 낮다. 「0 이상 30 미만」에 들지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 인화점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인화점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디에틸에테르&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−45 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;−30 [℃] 미만 — 맞다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세톤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−18 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;−30 이상 0 미만 — 맞다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벤젠&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−11 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0 이상 30 미만이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세트산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 40 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;30 이상 65 이하 — 맞다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;메탄올&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;11 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 구간에 드는 것은 메탄올·에탄올 쪽&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;벤젠의 인화점은 −11 [℃]&lt;/strong&gt;로 0 [℃]보다 낮다. 「0 이상 30 미만」에 들지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 인화점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인화점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디에틸에테르&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−45 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;−30 [℃] 미만 — 맞다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세톤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−18 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;−30 이상 0 미만 — 맞다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벤젠&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−11 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0 이상 30 미만이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세트산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 40 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;30 이상 65 이하 — 맞다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;메탄올&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;11 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 구간에 드는 것은 메탄올·에탄올 쪽&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>① 디에틸에테르는 −45 [℃] 로 −30 [℃] 미만이 맞다.&lt;br&gt;② 아세톤은 −18 [℃] 로 구간에 든다.&lt;br&gt;④ 아세트산은 약 40 [℃] 로 구간에 든다.</t>
+          <t>① 디에틸에테르는 −45 [℃]로 −30 [℃] 미만이 맞다.&lt;br&gt;② 아세톤은 −18 [℃]로 구간에 든다.&lt;br&gt;④ 아세트산은 약 40 [℃]로 구간에 든다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
@@ -12158,12 +12162,12 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>르 샤틀리에 식 $\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$ 다. 3:1 이므로 75 [%] 와 25 [%] 다. $\dfrac{100}{L} = \dfrac{75}{2.5} + \dfrac{25}{5.0} = 30 + 5 = 35$ 이므로 $L = 100 / 35 \fallingdotseq 2.9$ [vol%] 다.</t>
+          <t>르 샤틀리에 식 $\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$다. 3:1이므로 75 [%]와 25 [%]다. $\dfrac{100}{L} = \dfrac{75}{2.5} + \dfrac{25}{5.0} = 30 + 5 = 35$이므로 $L = 100 / 35 \fallingdotseq 2.9$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>② 3.3 은 계산과 맞지 않는다.&lt;br&gt;③ 3.8 도 맞지 않는다.&lt;br&gt;④ 4.0 은 단순 산술평균 쪽에 가깝다.</t>
+          <t>② 3.3은 계산과 맞지 않는다.&lt;br&gt;③ 3.8 도 맞지 않는다.&lt;br&gt;④ 4.0은 단순 산술평균 쪽에 가깝다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
@@ -12426,7 +12430,7 @@
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화의 조건&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt; 일 때 일어난다. 그래서 &lt;strong&gt;열이 나는 쪽을 키우는 인자&lt;/strong&gt;는 모두 「클수록」이고, &lt;strong&gt;열이 빠지는 쪽을 돕는 인자(열전도율·공기 유통)&lt;/strong&gt;만 「작을수록」이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;열전도율만 거꾸로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화의 조건&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt;일 때 일어난다. 그래서 &lt;strong&gt;열이 나는 쪽을 키우는 인자&lt;/strong&gt;는 모두 「클수록」이고, &lt;strong&gt;열이 빠지는 쪽을 돕는 인자(열전도율·공기 유통)&lt;/strong&gt;만 「작을수록」이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;열전도율만 거꾸로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12515,7 @@
       </c>
       <c r="U89" s="32" t="inlineStr">
         <is>
-          <t>메탄 1vol%, 헥산 2vol%, 에틸렌 2vol%, 공기 95vol%로 된 혼합가스의 폭발하한계값(vol%)은 약 얼마인가? (단, 메탄, 헥산, 에틸렌의 폭발하한계 값은 각각 5.0, 1.1, 2.7vol% 이다.)</t>
+          <t>메탄 1vol%, 헥산 2vol%, 에틸렌 2vol%, 공기 95vol%로 된 혼합가스의 폭발하한계값(vol%)은 약 얼마인가? (단, 메탄, 헥산, 에틸렌의 폭발하한계 값은 각각 5.0, 1.1, 2.7vol%이다.)</t>
         </is>
       </c>
       <c r="V89" s="32" t="inlineStr"/>
@@ -12545,17 +12549,17 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>가연성 가스만 100 [%] 로 환산한다. 합이 5 [%] 이므로 메탄 20, 헥산 40, 에틸렌 40 [%] 다. $\dfrac{100}{L} = \dfrac{20}{5.0} + \dfrac{40}{1.1} + \dfrac{40}{2.7} = 4 + 36.36 + 14.81 = 55.17$ 이므로 $L = 100 / 55.17 \fallingdotseq 1.8$ [vol%] 다.</t>
+          <t>가연성 가스만 100 [%]로 환산한다. 합이 5 [%]이므로 메탄 20, 헥산 40, 에틸렌 40 [%]다. $\dfrac{100}{L} = \dfrac{20}{5.0} + \dfrac{40}{1.1} + \dfrac{40}{2.7} = 4 + 36.36 + 14.81 = 55.17$이므로 $L = 100 / 55.17 \fallingdotseq 1.8$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>② 3.5 는 환산을 빼먹었을 때 쪽이다.&lt;br&gt;③ 12.8 은 자릿수가 어긋난다.&lt;br&gt;④ 21.7 도 맞지 않는다.</t>
+          <t>② 3.5는 환산을 빼먹었을 때 쪽이다.&lt;br&gt;③ 12.8은 자릿수가 어긋난다.&lt;br&gt;④ 21.7 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에의 혼합가스 폭발범위&lt;/strong&gt;&lt;br&gt;핵심은 &lt;strong&gt;공기를 뺀 가연성 가스끼리만 100 [%] 로 다시 나눈다&lt;/strong&gt;는 것이다. 이 환산을 빼먹으면 반드시 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기는 빼고 가연성끼리 100 으로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에의 혼합가스 폭발범위&lt;/strong&gt;&lt;br&gt;핵심은 &lt;strong&gt;공기를 뺀 가연성 가스끼리만 100 [%]로 다시 나눈다&lt;/strong&gt;는 것이다. 이 환산을 빼먹으면 반드시 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기는 빼고 가연성끼리 100으로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12932,12 +12936,12 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가열 매체의 온도가 위험물질의 분해온도보다 높은&lt;/strong&gt; 설비가 특수화학설비다. 나머지는 모두 기준에 못 미친다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;특수화학설비 여섯 가지 (규칙 제273조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설비&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발열반응&lt;/u&gt;이 일어나는 반응장치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흡열이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증류 · 정류 · 증발 · 추출&lt;/u&gt; 등 분리를 하는 장치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가열시켜 주는 물질의 온도가 가열되는 위험물질의 분해온도보다 높은&lt;/u&gt; 상태에서 운전되는 설비&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;온도·압력 기준과 달리 숫자가 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응폭주&lt;/u&gt; 등 이상 화학반응에 의해 위험물질이 발생할 우려가 있는 설비&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;온도가 350 [℃] 이상&lt;/u&gt; 이거나 &lt;u&gt;게이지 압력이 980 [kPa] 이상&lt;/u&gt;인 상태에서 운전되는 설비&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [℃] · 200 [kPa] 은 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가열로 또는 가열기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;가열 매체의 온도가 위험물질의 분해온도보다 높은&lt;/strong&gt; 설비가 특수화학설비다. 나머지는 모두 기준에 못 미친다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;특수화학설비 여섯 가지 (규칙 제273조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설비&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발열반응&lt;/u&gt;이 일어나는 반응장치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흡열이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증류 · 정류 · 증발 · 추출&lt;/u&gt; 등 분리를 하는 장치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가열시켜 주는 물질의 온도가 가열되는 위험물질의 분해온도보다 높은&lt;/u&gt; 상태에서 운전되는 설비&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;온도·압력 기준과 달리 숫자가 없다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응폭주&lt;/u&gt; 등 이상 화학반응에 의해 위험물질이 발생할 우려가 있는 설비&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;온도가 350 [℃] 이상&lt;/u&gt; 이거나 &lt;u&gt;게이지 압력이 980 [kPa] 이상&lt;/u&gt;인 상태에서 운전되는 설비&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [℃] · 200 [kPa]은 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가열로 또는 가열기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
         <is>
-          <t>② 게이지 압력 980 [kPa] 이상이라야 하므로 200 [kPa] 은 해당하지 않는다.&lt;br&gt;③ 온도 350 [℃] 이상이라야 하므로 300 [℃] 는 해당하지 않는다.&lt;br&gt;④ 흡열반응이 아니라 발열반응이 기준이다.</t>
+          <t>② 게이지 압력 980 [kPa] 이상이라야 하므로 200 [kPa]은 해당하지 않는다.&lt;br&gt;③ 온도 350 [℃] 이상이라야 하므로 300 [℃]는 해당하지 않는다.&lt;br&gt;④ 흡열반응이 아니라 발열반응이 기준이다.</t>
         </is>
       </c>
       <c r="AI92" s="32" t="inlineStr">
@@ -13061,12 +13065,12 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>노출지수는 $200 / 500 + 100 / 200 = 0.4 + 0.5 = 0.9$ 다. 혼합물의 허용농도는 $\dfrac{\text{실제 농도의 합}}{\text{노출지수}} = \dfrac{200 + 100}{0.9} = \dfrac{300}{0.9} \fallingdotseq 333$ [ppm] 이다.</t>
+          <t>노출지수는 $200 / 500 + 100 / 200 = 0.4 + 0.5 = 0.9$다. 혼합물의 허용농도는 $\dfrac{\text{실제 농도의 합}}{\text{노출지수}} = \dfrac{200 + 100}{0.9} = \dfrac{300}{0.9} \fallingdotseq 333$ [ppm]이다.</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>① 150 [ppm] 은 계산과 맞지 않는다.&lt;br&gt;② 200 [ppm] 도 맞지 않는다.&lt;br&gt;③ 270 [ppm] 은 노출지수를 곱했을 때 쪽이다.</t>
+          <t>① 150 [ppm]은 계산과 맞지 않는다.&lt;br&gt;② 200 [ppm] 도 맞지 않는다.&lt;br&gt;③ 270 [ppm]은 노출지수를 곱했을 때 쪽이다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13577,17 +13581,17 @@
       </c>
       <c r="AG97" s="32" t="inlineStr">
         <is>
-          <t>5 [%] 를 $x$ [kg] 이라 하면 10 [%] 는 $100 - x$ 다. NaOH 의 양으로 식을 세우면 $0.05 x + 0.10 ( 100 - x ) = 0.06 \times 100$ 이다. $10 - 0.05 x = 6$ 이므로 $x = 80$ 이다. 곧 &lt;strong&gt;5 [%] 80 [kg], 10 [%] 20 [kg]&lt;/strong&gt;이다.</t>
+          <t>5 [%]를 $x$ [kg]이라 하면 10 [%]는 $100 - x$다. NaOH의 양으로 식을 세우면 $0.05 x + 0.10 ( 100 - x ) = 0.06 \times 100$이다. $10 - 0.05 x = 6$이므로 $x = 80$이다. 곧 &lt;strong&gt;5 [%] 80 [kg], 10 [%] 20 [kg]&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH97" s="32" t="inlineStr">
         <is>
-          <t>① 33.3 / 66.7 은 목표 농도가 8 [%] 를 넘을 때의 비다.&lt;br&gt;② 50 / 50 이면 농도가 7.5 [%] 가 된다.&lt;br&gt;③ 66.7 / 33.3 이면 농도가 약 6.7 [%] 가 된다.</t>
+          <t>① 33.3 / 66.7은 목표 농도가 8 [%]를 넘을 때의 비다.&lt;br&gt;② 50 / 50 이면 농도가 7.5 [%]가 된다.&lt;br&gt;③ 66.7 / 33.3 이면 농도가 약 6.7 [%]가 된다.</t>
         </is>
       </c>
       <c r="AI97" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;물질수지(mass balance)&lt;/strong&gt;&lt;br&gt;목표 농도 6 [%] 가 &lt;strong&gt;5 와 10 가운데 5 쪽에 훨씬 가까우므로&lt;/strong&gt;, 계산하기 전에도 &lt;strong&gt;5 [%] 용액이 훨씬 많이&lt;/strong&gt; 들어간다는 것을 알 수 있다. 이 감으로 보기 둘을 미리 거를 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용질의 양으로 식을 세운다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;물질수지(mass balance)&lt;/strong&gt;&lt;br&gt;목표 농도 6 [%]가 &lt;strong&gt;5와 10 가운데 5 쪽에 훨씬 가까우므로&lt;/strong&gt;, 계산하기 전에도 &lt;strong&gt;5 [%] 용액이 훨씬 많이&lt;/strong&gt; 들어간다는 것을 알 수 있다. 이 감으로 보기 둘을 미리 거를 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용질의 양으로 식을 세운다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13716,7 +13720,7 @@
       </c>
       <c r="AI98" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;펌프의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;왕복이냐 회전이냐&lt;/strong&gt;는 「무엇이 움직이는가」로 갈린다. 둘 다 &lt;strong&gt;용적형&lt;/strong&gt;이라 &lt;strong&gt;토출 쪽을 막으면 압력이 급상승&lt;/strong&gt; 하므로 &lt;strong&gt;안전밸브가 반드시&lt;/strong&gt; 필요하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;기어 펌프만 회전펌프&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;펌프의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;왕복이냐 회전이냐&lt;/strong&gt;는 「무엇이 움직이는가」로 갈린다. 둘 다 &lt;strong&gt;용적형&lt;/strong&gt;이라 &lt;strong&gt;토출 쪽을 막으면 압력이 급상승&lt;/strong&gt;하므로 &lt;strong&gt;안전밸브가 반드시&lt;/strong&gt; 필요하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;기어 펌프만 회전펌프&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14093,17 +14097,17 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>$H = \dfrac{U - L}{L} = \dfrac{74 - 12.5}{12.5} = \dfrac{61.5}{12.5} = 4.92$ 다.</t>
+          <t>$H = \dfrac{U - L}{L} = \dfrac{74 - 12.5}{12.5} = \dfrac{61.5}{12.5} = 4.92$다.</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>② 5.26 은 분모를 잘못 잡았을 때 나온다.&lt;br&gt;③ 6.26 도 계산과 맞지 않는다.&lt;br&gt;④ 7.05 도 맞지 않는다.</t>
+          <t>② 5.26은 분모를 잘못 잡았을 때 나온다.&lt;br&gt;③ 6.26 도 계산과 맞지 않는다.&lt;br&gt;④ 7.05 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가스의 위험도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 하한&lt;/strong&gt;이다. 일산화탄소는 폭발범위가 넓지만 &lt;strong&gt;하한이 12.5 [%] 로 높아&lt;/strong&gt; 위험도는 4.92 로 중간쯤이다. 아세틸렌(31.4)이나 수소(17.8)보다 훨씬 낮다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = ( U - L ) / L$ — &lt;u&gt;분모는 하한&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가스의 위험도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 하한&lt;/strong&gt;이다. 일산화탄소는 폭발범위가 넓지만 &lt;strong&gt;하한이 12.5 [%]로 높아&lt;/strong&gt; 위험도는 4.92로 중간쯤이다. 아세틸렌(31.4)이나 수소(17.8)보다 훨씬 낮다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = ( U - L ) / L$ — &lt;u&gt;분모는 하한&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14480,7 +14484,7 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;75° 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;말비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재와 수평면의 기울기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재와 수평면의 각도가 75° 이하일 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보조부재&lt;/u&gt; 설치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다리가 벌어지지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 2 [m] 를 초과할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업발판 폭 &lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밑부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미끄럼 방지장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;75° 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;말비계의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재와 수평면의 기울기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지주부재와 수평면의 각도가 75° 이하일 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;보조부재&lt;/u&gt; 설치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다리가 벌어지지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 2 [m]를 초과할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업발판 폭 &lt;u&gt;40 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;밑부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미끄럼 방지장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
@@ -14619,7 +14623,7 @@
       </c>
       <c r="AI105" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;NATM 공법의 계측&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;NATM&lt;/strong&gt;은 &lt;strong&gt;지반 자체를 지보재로 삼는&lt;/strong&gt; 공법이라, &lt;strong&gt;록 볼트와 숏크리트로 원지반을 보강&lt;/strong&gt; 하고 &lt;strong&gt;계측으로 그 효과를 끊임없이 확인&lt;/strong&gt; 한다. 계측이 공법의 일부다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내공변위 · 천단침하 · 인발시험&lt;/u&gt; — 진동은 발파 쪽.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;NATM 공법의 계측&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;NATM&lt;/strong&gt;은 &lt;strong&gt;지반 자체를 지보재로 삼는&lt;/strong&gt; 공법이라, &lt;strong&gt;록 볼트와 숏크리트로 원지반을 보강&lt;/strong&gt;하고 &lt;strong&gt;계측으로 그 효과를 끊임없이 확인&lt;/strong&gt;한다. 계측이 공법의 일부다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내공변위 · 천단침하 · 인발시험&lt;/u&gt; — 진동은 발파 쪽.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14743,12 +14747,12 @@
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① 100 [kgf] 는 기준에 못 미친다.&lt;br&gt;③ 300 [kgf] 는 기준보다 크다.&lt;br&gt;④ 400 [kgf] 도 기준이 아니다.</t>
+          <t>① 100 [kgf]는 기준에 못 미친다.&lt;br&gt;③ 300 [kgf]는 기준보다 크다.&lt;br&gt;④ 400 [kgf] 도 기준이 아니다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;추락재해방지 표준안전작업지침 — 방망사의 인장강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;매듭 없는 쪽이 요구 강도가 더 높다&lt;/strong&gt;(240 &amp;gt; 200). 매듭이 없으면 힘이 한 가닥에 몰리기 때문이다. &lt;strong&gt;정기시험은 사용 개시 후 1년 이내, 그 뒤 6개월마다&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;10 [cm] — 매듭 없음 240, 매듭 있음 200&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;추락재해방지 표준안전작업지침 — 방망사의 인장강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;매듭 없는 쪽이 요구 강도가 더 높다&lt;/strong&gt;(240 &amp;gt; 200). 매듭이 없으면 힘이 한 가닥에 몰리기 때문이다. &lt;strong&gt;정기시험은 사용 개시 후 1년 이내, 그 뒤 6개월마다&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;10 [cm] — 매듭 없음 240, 매듭 있음 200&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15004,12 +15008,12 @@
       </c>
       <c r="AG108" s="32" t="inlineStr">
         <is>
-          <t>출제 당시 기준으로 &lt;strong&gt;보통흙 습지는 1 : 1 ~ 1 : 1.5&lt;/strong&gt; 였다. 다만 &lt;strong&gt;현행 기준은 다르다&lt;/strong&gt;. 아래 주의사항을 반드시 함께 보아야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;굴착면의 기울기 — 옛 기준과 현행&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지반&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;옛 기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;u&gt;현행 (2021. 11. 19. 개정)&lt;/u&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보통흙 습지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1 ~ 1 : 1.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「그 밖의 흙」 1 : 1.2 로 통합&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보통흙 건지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 : 0.5 ~ 1 : 1&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「그 밖의 흙」 1 : 1.2 로 통합&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;모래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 : 1.8&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.8&lt;/u&gt; — 그대로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍화암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 : 1.0&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「연암 및 풍화암」 1 : 1.0&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.0 으로 완만해짐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 : 0.5&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt; — 그대로&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>출제 당시 기준으로 &lt;strong&gt;보통흙 습지는 1 : 1 ~ 1 : 1.5&lt;/strong&gt; 였다. 다만 &lt;strong&gt;현행 기준은 다르다&lt;/strong&gt;. 아래 주의사항을 반드시 함께 보아야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;굴착면의 기울기 — 옛 기준과 현행&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지반&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;옛 기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;u&gt;현행 (2021. 11. 19. 개정)&lt;/u&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보통흙 습지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1 ~ 1 : 1.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「그 밖의 흙」 1 : 1.2로 통합&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보통흙 건지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 : 0.5 ~ 1 : 1&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「그 밖의 흙」 1 : 1.2로 통합&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;모래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 : 1.8&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.8&lt;/u&gt; — 그대로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍화암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 : 1.0&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「연암 및 풍화암」 1 : 1.0&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 1.0으로 완만해짐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경암&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1 : 0.5&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt; — 그대로&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH108" s="32" t="inlineStr">
         <is>
-          <t>① 1 : 0.5 ~ 1 : 1 은 옛 기준의 보통흙 건지다.&lt;br&gt;③ 1 : 0.8 은 어느 기준에도 없다.&lt;br&gt;④ 1 : 0.5 는 경암의 기준이다.</t>
+          <t>① 1 : 0.5 ~ 1 : 1은 옛 기준의 보통흙 건지다.&lt;br&gt;③ 1 : 0.8은 어느 기준에도 없다.&lt;br&gt;④ 1 : 0.5는 경암의 기준이다.</t>
         </is>
       </c>
       <c r="AI108" s="32" t="inlineStr">
@@ -15133,12 +15137,12 @@
       </c>
       <c r="AG109" s="32" t="inlineStr">
         <is>
-          <t>공정률 &lt;strong&gt;50 [%] 이상 70 [%] 미만&lt;/strong&gt; 구간이므로 &lt;strong&gt;50 [%] 이상&lt;/strong&gt;을 써야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;공사 진척에 따른 산업안전보건관리비 사용기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공정률&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소 사용기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [%] 이상 70 [%] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;공정률 65 [%] 가 여기 든다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;70 [%] 이상 90 [%] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;70 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;90 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>공정률 &lt;strong&gt;50 [%] 이상 70 [%] 미만&lt;/strong&gt; 구간이므로 &lt;strong&gt;50 [%] 이상&lt;/strong&gt;을 써야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;공사 진척에 따른 산업안전보건관리비 사용기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;공정률&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소 사용기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [%] 이상 70 [%] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;공정률 65 [%]가 여기 든다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;70 [%] 이상 90 [%] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;70 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;90 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH109" s="32" t="inlineStr">
         <is>
-          <t>① 40 [%] 라는 기준 구간은 없다.&lt;br&gt;③ 60 [%] 도 기준값이 아니다.&lt;br&gt;④ 70 [%] 는 공정률 70 [%] 이상일 때다.</t>
+          <t>① 40 [%]라는 기준 구간은 없다.&lt;br&gt;③ 60 [%] 도 기준값이 아니다.&lt;br&gt;④ 70 [%]는 공정률 70 [%] 이상일 때다.</t>
         </is>
       </c>
       <c r="AI109" s="32" t="inlineStr">
@@ -15391,17 +15395,17 @@
       </c>
       <c r="AG111" s="32" t="inlineStr">
         <is>
-          <t>옛 기준으로 보통흙 건지는 &lt;strong&gt;1 : 0.5 ~ 1 : 1&lt;/strong&gt;이다. 1 : 0.3 이 아니다. 다만 &lt;strong&gt;현행 기준은 「보통흙」 구분 자체가 없다&lt;/strong&gt;.</t>
+          <t>옛 기준으로 보통흙 건지는 &lt;strong&gt;1 : 0.5 ~ 1 : 1&lt;/strong&gt;이다. 1 : 0.3이 아니다. 다만 &lt;strong&gt;현행 기준은 「보통흙」 구분 자체가 없다&lt;/strong&gt;.</t>
         </is>
       </c>
       <c r="AH111" s="32" t="inlineStr">
         <is>
-          <t>① 보통흙 습지 1 : 1 ~ 1 : 1.5 는 옛 기준으로 맞다.&lt;br&gt;③ 풍화암 1 : 1.0 은 맞다.&lt;br&gt;④ 연암 1 : 1.0 은 현행 기준으로 맞다.</t>
+          <t>① 보통흙 습지 1 : 1 ~ 1 : 1.5는 옛 기준으로 맞다.&lt;br&gt;③ 풍화암 1 : 1.0은 맞다.&lt;br&gt;④ 연암 1 : 1.0은 현행 기준으로 맞다.</t>
         </is>
       </c>
       <c r="AI111" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 별표11 — 굴착면의 기울기 기준&lt;/strong&gt;&lt;br&gt;앞 문항과 짝이다. 현행 네 줄 — &lt;strong&gt;모래 1:1.8 · 연암 및 풍화암 1:1.0 · 경암 1:0.5 · 그 밖의 흙 1:1.2&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;보통흙 건지는 0.5 부터&lt;/u&gt; — 0.3 이 아니다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 11. 19. 개정&lt;/u&gt;으로 「보통흙 습지·건지」 구분이 사라지고 &lt;u&gt;「그 밖의 흙」 1 : 1.2&lt;/u&gt;로 묶였다. 따라서 &lt;u&gt;현행 기준으로는 ①도 옳지 않다&lt;/u&gt;. &lt;u&gt;옛 기준으로 푸는 문항&lt;/u&gt; 임을 알고 넘어가야 한다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 11&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 별표11 — 굴착면의 기울기 기준&lt;/strong&gt;&lt;br&gt;앞 문항과 짝이다. 현행 네 줄 — &lt;strong&gt;모래 1:1.8 · 연암 및 풍화암 1:1.0 · 경암 1:0.5 · 그 밖의 흙 1:1.2&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;보통흙 건지는 0.5부터&lt;/u&gt; — 0.3이 아니다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 11. 19. 개정&lt;/u&gt;으로 「보통흙 습지·건지」 구분이 사라지고 &lt;u&gt;「그 밖의 흙」 1 : 1.2&lt;/u&gt;로 묶였다. 따라서 &lt;u&gt;현행 기준으로는 ①도 옳지 않다&lt;/u&gt;. &lt;u&gt;옛 기준으로 푸는 문항&lt;/u&gt; 임을 알고 넘어가야 한다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 11&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -15649,7 +15653,7 @@
       </c>
       <c r="AG113" s="32" t="inlineStr">
         <is>
-          <t>달기강대와 상하부 지점의 안전계수는 &lt;strong&gt;강재 2.5 이상&lt;/strong&gt;이다. 3 이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;달비계의 안전계수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;부재&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전계수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달기 와이어로프 · 달기 강선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달기 체인 · 달기 훅&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달기 강대와 상·하부 지점 — 강재&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 작다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달기 강대와 상·하부 지점 — 목재&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>달기강대와 상하부 지점의 안전계수는 &lt;strong&gt;강재 2.5 이상&lt;/strong&gt;이다. 3이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;달비계의 안전계수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;부재&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전계수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달기 와이어로프 · 달기 강선&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달기 체인 · 달기 훅&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달기 강대와 상·하부 지점 — 강재&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가장 작다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;달기 강대와 상·하부 지점 — 목재&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH113" s="32" t="inlineStr">
@@ -15659,7 +15663,7 @@
       </c>
       <c r="AI113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제55조 — 달비계의 안전계수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람이 매달리는 줄일수록 안전계수가 크다&lt;/strong&gt;. 그래서 와이어로프가 10 으로 가장 크고, 구조 부재인 강대는 2.5 로 가장 작다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;10 · 5 · 2.5(강재) · 5(목재)&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C55%EC%A1%B0" target="_blank"&gt;제55조(작업발판의 최대적재하중)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제55조(작업발판의 최대적재하중) 사업주는 비계의 구조 및 재료에 따라 작업발판의 최대적재하중을 정하고, 이를 초과하여 실어서는 안 된다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제55조 — 달비계의 안전계수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람이 매달리는 줄일수록 안전계수가 크다&lt;/strong&gt;. 그래서 와이어로프가 10으로 가장 크고, 구조 부재인 강대는 2.5로 가장 작다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;10 · 5 · 2.5(강재) · 5(목재)&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C55%EC%A1%B0" target="_blank"&gt;제55조(작업발판의 최대적재하중)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;제55조(작업발판의 최대적재하중) 사업주는 비계의 구조 및 재료에 따라 작업발판의 최대적재하중을 정하고, 이를 초과하여 실어서는 안 된다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -15778,7 +15782,7 @@
       </c>
       <c r="AG114" s="32" t="inlineStr">
         <is>
-          <t>발끝막이판(폭목)은 &lt;strong&gt;10 [cm] 이상&lt;/strong&gt;이다. 20 [cm] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부 난간대 · 중간 난간대 · 발끝막이판 · 난간기둥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;네 가지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부 난간대 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 90 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120 [cm] 이하면 중간 난간대 1개&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상부 난간대와 바닥의 &lt;u&gt;중간에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120 [cm] 초과면 &lt;u&gt;60 [cm] 이하마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;폭목이라고도 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간대 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.7 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;금속제 파이프&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [kg] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 취약한 방향으로&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>발끝막이판(폭목)은 &lt;strong&gt;10 [cm] 이상&lt;/strong&gt;이다. 20 [cm]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부 난간대 · 중간 난간대 · 발끝막이판 · 난간기둥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;네 가지&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부 난간대 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 90 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120 [cm] 이하면 중간 난간대 1개&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상부 난간대와 바닥의 &lt;u&gt;중간에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120 [cm] 초과면 &lt;u&gt;60 [cm] 이하마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;폭목이라고도 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간대 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.7 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;금속제 파이프&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [kg] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 취약한 방향으로&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH114" s="32" t="inlineStr">
@@ -15788,7 +15792,7 @@
       </c>
       <c r="AI114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제13조 — 안전난간의 구조 및 설치요건&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;상부 난간대는 90 [cm] 이상&lt;/strong&gt;이며 &lt;strong&gt;상한은 없다&lt;/strong&gt;. 120 [cm] 는 &lt;strong&gt;중간 난간대를 몇 개 둘 것인가&lt;/strong&gt;를 가르는 분기점일 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;난간 90 이상, 폭목 10 이상, 지름 2.7, 하중 100&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C13%EC%A1%B0" target="_blank"&gt;제13조(안전난간의 구조 및 설치요건)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 근로자의 추락 등의 위험을 방지하기 위하여 안전난간을 설치하는 경우 다음 각 호의 기준에 맞는 구조로 설치해야 한다. &amp;lt;개정 2015.12.31, 2023.11.14&amp;gt;&lt;br&gt; 1. 상부 난간대, 중간 난간대, 발끝막이판 및 난간기둥으로 구성할 것. 다만, 중간 난간대, 발끝막이판 및 난간기둥은 이와 비슷한 구조와 성능을 가진 것으로 대체할 수 있다.&lt;br&gt;▶  2. &lt;strong&gt;상부 난간대는&lt;/strong&gt; 바닥면ㆍ발판 또는 경사로의 표면(이하 "바닥면등"이라 한다)으로부터 90센티미터 이상 지점에 설치하고, 상부 난간대를 120센티미터 이하에 설치하는 경우에는 중간 난간대는 상부 난간대와 바닥면등의 중간에 설치해야 하며, 120센티미터 이상 지점에 설치하는 경우에는 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 2단 이상으로 균등하게 설치하고 난간의 상하 간격은 60센티미터 이하가 되도록 할 것. 다만, 난간기둥 간의 간격이 25센티미터 이하인 경우에는 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 설치하지 않을 수 있다.&lt;br&gt;▶  3. 발끝막이판은 바닥면등으로부터 10센티미터 이상의 &lt;strong&gt;높이를 유지할 것&lt;/strong&gt;. 다만, 물체가 떨어지거나 날아올 위험이 없거나 그 위험을 방지할 수 있는 망을 설치하는 등 필요한 예방 조치를 한 장소는 제외한다.&lt;br&gt;▶  4. 난간기둥은 상부 난간대와 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 견고하게 떠받칠 수 있도록 적정한 간격을 유지할 것&lt;br&gt; 5. 상부 난간대와 중간 난간대는 난간 길이 전체에 걸쳐 바닥면등과 평행을 유지할 것&lt;br&gt; 6. 난간대는 지름 2.7센티미터 이상의 금속제 파이프나 그 이상의 강도가 있는 재료일 것&lt;br&gt; 7. 안전난간은 구조적으로 가장 취약한 지점에서 가장 취약한 방향으로 작용하는 100킬로그램 이상의 하중에 견딜 수 있는 튼튼한 구조일 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제13조 — 안전난간의 구조 및 설치요건&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;상부 난간대는 90 [cm] 이상&lt;/strong&gt;이며 &lt;strong&gt;상한은 없다&lt;/strong&gt;. 120 [cm]는 &lt;strong&gt;중간 난간대를 몇 개 둘 것인가&lt;/strong&gt;를 가르는 분기점일 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;난간 90 이상, 폭목 10 이상, 지름 2.7, 하중 100&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C13%EC%A1%B0" target="_blank"&gt;제13조(안전난간의 구조 및 설치요건)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 근로자의 추락 등의 위험을 방지하기 위하여 안전난간을 설치하는 경우 다음 각 호의 기준에 맞는 구조로 설치해야 한다. &amp;lt;개정 2015.12.31, 2023.11.14&amp;gt;&lt;br&gt; 1. 상부 난간대, 중간 난간대, 발끝막이판 및 난간기둥으로 구성할 것. 다만, 중간 난간대, 발끝막이판 및 난간기둥은 이와 비슷한 구조와 성능을 가진 것으로 대체할 수 있다.&lt;br&gt;▶  2. &lt;strong&gt;상부 난간대는&lt;/strong&gt; 바닥면ㆍ발판 또는 경사로의 표면(이하 "바닥면등"이라 한다)으로부터 90센티미터 이상 지점에 설치하고, 상부 난간대를 120센티미터 이하에 설치하는 경우에는 중간 난간대는 상부 난간대와 바닥면등의 중간에 설치해야 하며, 120센티미터 이상 지점에 설치하는 경우에는 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 2단 이상으로 균등하게 설치하고 난간의 상하 간격은 60센티미터 이하가 되도록 할 것. 다만, 난간기둥 간의 간격이 25센티미터 이하인 경우에는 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 설치하지 않을 수 있다.&lt;br&gt;▶  3. 발끝막이판은 바닥면등으로부터 10센티미터 이상의 &lt;strong&gt;높이를 유지할 것&lt;/strong&gt;. 다만, 물체가 떨어지거나 날아올 위험이 없거나 그 위험을 방지할 수 있는 망을 설치하는 등 필요한 예방 조치를 한 장소는 제외한다.&lt;br&gt;▶  4. 난간기둥은 상부 난간대와 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 견고하게 떠받칠 수 있도록 적정한 간격을 유지할 것&lt;br&gt; 5. 상부 난간대와 중간 난간대는 난간 길이 전체에 걸쳐 바닥면등과 평행을 유지할 것&lt;br&gt; 6. 난간대는 지름 2.7센티미터 이상의 금속제 파이프나 그 이상의 강도가 있는 재료일 것&lt;br&gt; 7. 안전난간은 구조적으로 가장 취약한 지점에서 가장 취약한 방향으로 작용하는 100킬로그램 이상의 하중에 견딜 수 있는 튼튼한 구조일 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16175,7 +16179,7 @@
       </c>
       <c r="AI117" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제332조 — 거푸집 동바리 조립 시 안전조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;맞댄이음과 장부이음&lt;/strong&gt;은 축력이 &lt;strong&gt;한 직선으로 곧게 전달되는&lt;/strong&gt; 이음이다. 어긋나게 잇거나 겹쳐 대면 &lt;strong&gt;편심이 생겨 좌굴&lt;/strong&gt; 한다. 그래서 이 둘로 하라는 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맞댄이음·장부이음은 「하라」는 것&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C332%EC%A1%B0" target="_blank"&gt;제332조(동바리 조립 시의 안전조치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 동바리를 조립하는 경우에는 하중의 지지상태를 유지할 수 있도록 다음 각 호의 사항을 준수해야 한다.&lt;br&gt; 1. 받침목이나 깔판의 사용, 콘크리트 타설, 말뚝박기 등 동바리의 침하를 방지하기 위한 조치를 할 것&lt;br&gt; 2. 동바리의 상하 고정 및 미끄러짐 방지 조치를 할 것&lt;br&gt; 3. 상부ㆍ하부의 동바리가 동일 수직선상에 위치하도록 하여 깔판ㆍ받침목에 고정시킬 것&lt;br&gt; 4. 개구부 상부에 동바리를 설치하는 경우에는 상부하중을 견딜 수 있는 견고한 받침대를 설치할 것&lt;br&gt; 5. U헤드 등의 단판이 없는 동바리의 상단에 멍에 등을 올릴 경우에는 해당 상단에 U헤드 등의 단판을 설치하고, 멍에 등이 전도되거나 이탈되지 않도록 고정시킬 것&lt;br&gt;▶  6. &lt;strong&gt;동바리의 이음은&lt;/strong&gt; 같은 품질의 재료를 사용할 것&lt;br&gt; 7. 강재의 접속부 및 교차부는 볼트ㆍ클램프 등 전용철물을 사용하여 단단히 연결할 것&lt;br&gt; 8. 거푸집의 형상에 따른 부득이한 경우를 제외하고는 깔판이나 받침목은 2단 이상 끼우지 않도록 할 것&lt;br&gt; 9. 깔판이나 받침목을 이어서 사용하는 경우에는 그 깔판ㆍ받침목을 단단히 연결할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제332조 — 거푸집 동바리 조립 시 안전조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;맞댄이음과 장부이음&lt;/strong&gt;은 축력이 &lt;strong&gt;한 직선으로 곧게 전달되는&lt;/strong&gt; 이음이다. 어긋나게 잇거나 겹쳐 대면 &lt;strong&gt;편심이 생겨 좌굴&lt;/strong&gt;한다. 그래서 이 둘로 하라는 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;맞댄이음·장부이음은 「하라」는 것&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C332%EC%A1%B0" target="_blank"&gt;제332조(동바리 조립 시의 안전조치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 동바리를 조립하는 경우에는 하중의 지지상태를 유지할 수 있도록 다음 각 호의 사항을 준수해야 한다.&lt;br&gt; 1. 받침목이나 깔판의 사용, 콘크리트 타설, 말뚝박기 등 동바리의 침하를 방지하기 위한 조치를 할 것&lt;br&gt; 2. 동바리의 상하 고정 및 미끄러짐 방지 조치를 할 것&lt;br&gt; 3. 상부ㆍ하부의 동바리가 동일 수직선상에 위치하도록 하여 깔판ㆍ받침목에 고정시킬 것&lt;br&gt; 4. 개구부 상부에 동바리를 설치하는 경우에는 상부하중을 견딜 수 있는 견고한 받침대를 설치할 것&lt;br&gt; 5. U헤드 등의 단판이 없는 동바리의 상단에 멍에 등을 올릴 경우에는 해당 상단에 U헤드 등의 단판을 설치하고, 멍에 등이 전도되거나 이탈되지 않도록 고정시킬 것&lt;br&gt;▶  6. &lt;strong&gt;동바리의 이음은&lt;/strong&gt; 같은 품질의 재료를 사용할 것&lt;br&gt; 7. 강재의 접속부 및 교차부는 볼트ㆍ클램프 등 전용철물을 사용하여 단단히 연결할 것&lt;br&gt; 8. 거푸집의 형상에 따른 부득이한 경우를 제외하고는 깔판이나 받침목은 2단 이상 끼우지 않도록 할 것&lt;br&gt; 9. 깔판이나 받침목을 이어서 사용하는 경우에는 그 깔판ㆍ받침목을 단단히 연결할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16433,7 +16437,7 @@
       </c>
       <c r="AI119" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제322조 — 충전전로 인근에서의 차량·기계장치 작업&lt;/strong&gt;&lt;br&gt;충전전로에서 &lt;strong&gt;차량이나 기계장치는 10 [m] 이상 떨어져야&lt;/strong&gt; 하며, &lt;strong&gt;대지전압이 50 [kV] 를 넘으면 10 [kV] 마다 10 [cm] 씩 더&lt;/strong&gt; 띄운다. 절연용 방호구를 설치했다면 접촉 한계거리까지 접근할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전선 밑에는 세워 두지 않는다&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C322%EC%A1%B0" target="_blank"&gt;제322조(충전전로 인근에서의 차량ㆍ기계장치 작업)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 충전전로 인근에서 차량, 기계장치 등(이하 이 조에서 "차량등"이라 한다)의 작업이 있는 경우에는 차량등을 충전전로의 충전부로부터 300센티미터 이상 이격시켜 유지시키되, &lt;strong&gt;대지전압이 50&lt;/strong&gt;킬로볼트를 넘는 경우 이격시켜 유지하여야 하는 거리(이하 이 조에서 "이격거리"라 한다)는 10킬로볼트 증가할 때마다 10센티미터씩 증가시켜야 한다. 다만, 차량등의 높이를 낮춘 상태에서 이동하는 경우에는 이격거리를 120센티미터 이상(&lt;strong&gt;대지전압이 50&lt;/strong&gt;킬로볼트를 넘는 경우에는 10킬로볼트 증가할 때마다 이격거리를 10센티미터씩 증가)으로 할 수 있다.&lt;br&gt;② 제1항에도 불구하고 충전전로의 전압에 적합한 절연용 방호구 등을 설치한 경우에는 이격거리를 절연용 방호구 앞면까지로 할 수 있으며, 차량등의 가공 붐대의 버킷이나 끝부분 등이 충전전로의 전압에 적합하게 절연되어 있고 유자격자가 작업을 수행하는 경우에는 붐대의 절연되지 않은 부분과 충전전로 간의 이격거리는 제321조제1항제8호의 표에 따른 접근 한계거리까지로 할 수 있다. &amp;lt;개정 2021.5.28&amp;gt;&lt;br&gt;③ 사업주는 다음 각 호의 경우를 제외하고는 근로자가 차량등의 그 어느 부분과도 접촉하지 않도록 울타리를 설치하거나 감시인 배치 등의 조치를 하여야 한다. &amp;lt;개정 2019.10.15&amp;gt;&lt;br&gt; 1. 근로자가 해당 전압에 적합한 제323조제1항의 절연용 보호구등을 착용하거나 사용하는 경우&lt;br&gt; 2. 차량등의 절연되지 않은 부분이 제321조제1항의 표에 따른 접근 한계거리 이내로 접근하지 않도록 하는 경우&lt;br&gt;④ 사업주는 충전전로 인근에서 접지된 차량등이 충전전로와 접촉할 우려가 있을 경우에는 지상의 근로자가 접지점에 접촉하지 않도록 조치하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제322조 — 충전전로 인근에서의 차량·기계장치 작업&lt;/strong&gt;&lt;br&gt;충전전로에서 &lt;strong&gt;차량이나 기계장치는 10 [m] 이상 떨어져야&lt;/strong&gt; 하며, &lt;strong&gt;대지전압이 50 [kV]를 넘으면 10 [kV] 마다 10 [cm] 씩 더&lt;/strong&gt; 띄운다. 절연용 방호구를 설치했다면 접촉 한계거리까지 접근할 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전선 밑에는 세워 두지 않는다&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C322%EC%A1%B0" target="_blank"&gt;제322조(충전전로 인근에서의 차량ㆍ기계장치 작업)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 충전전로 인근에서 차량, 기계장치 등(이하 이 조에서 "차량등"이라 한다)의 작업이 있는 경우에는 차량등을 충전전로의 충전부로부터 300센티미터 이상 이격시켜 유지시키되, &lt;strong&gt;대지전압이 50&lt;/strong&gt;킬로볼트를 넘는 경우 이격시켜 유지하여야 하는 거리(이하 이 조에서 "이격거리"라 한다)는 10킬로볼트 증가할 때마다 10센티미터씩 증가시켜야 한다. 다만, 차량등의 높이를 낮춘 상태에서 이동하는 경우에는 이격거리를 120센티미터 이상(&lt;strong&gt;대지전압이 50&lt;/strong&gt;킬로볼트를 넘는 경우에는 10킬로볼트 증가할 때마다 이격거리를 10센티미터씩 증가)으로 할 수 있다.&lt;br&gt;② 제1항에도 불구하고 충전전로의 전압에 적합한 절연용 방호구 등을 설치한 경우에는 이격거리를 절연용 방호구 앞면까지로 할 수 있으며, 차량등의 가공 붐대의 버킷이나 끝부분 등이 충전전로의 전압에 적합하게 절연되어 있고 유자격자가 작업을 수행하는 경우에는 붐대의 절연되지 않은 부분과 충전전로 간의 이격거리는 제321조제1항제8호의 표에 따른 접근 한계거리까지로 할 수 있다. &amp;lt;개정 2021.5.28&amp;gt;&lt;br&gt;③ 사업주는 다음 각 호의 경우를 제외하고는 근로자가 차량등의 그 어느 부분과도 접촉하지 않도록 울타리를 설치하거나 감시인 배치 등의 조치를 하여야 한다. &amp;lt;개정 2019.10.15&amp;gt;&lt;br&gt; 1. 근로자가 해당 전압에 적합한 제323조제1항의 절연용 보호구등을 착용하거나 사용하는 경우&lt;br&gt; 2. 차량등의 절연되지 않은 부분이 제321조제1항의 표에 따른 접근 한계거리 이내로 접근하지 않도록 하는 경우&lt;br&gt;④ 사업주는 충전전로 인근에서 접지된 차량등이 충전전로와 접촉할 우려가 있을 경우에는 지상의 근로자가 접지점에 접촉하지 않도록 조치하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -16681,12 +16685,12 @@
       </c>
       <c r="AG121" s="32" t="inlineStr">
         <is>
-          <t>$\text{안전계수} = \dfrac{\text{절단하중}}{\text{최대하중}}$ 이므로 $\text{최대하중} = 200 / 5 = 40$ [ton] 이다.</t>
+          <t>$\text{안전계수} = \dfrac{\text{절단하중}}{\text{최대하중}}$이므로 $\text{최대하중} = 200 / 5 = 40$ [ton]이다.</t>
         </is>
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>① 1,000톤은 나누지 않고 곱한 값이다.&lt;br&gt;② 400톤은 계산과 맞지 않는다.&lt;br&gt;③ 100톤은 안전계수를 2 로 잡았을 때다.</t>
+          <t>① 1,000톤은 나누지 않고 곱한 값이다.&lt;br&gt;② 400톤은 계산과 맞지 않는다.&lt;br&gt;③ 100톤은 안전계수를 2로 잡았을 때다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
